--- a/week-01/Ex2B_data_roundup.xlsx
+++ b/week-01/Ex2B_data_roundup.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jimmy\OneDrive\Desktop\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7087E1AE-7998-4A81-AB07-75C1CB1FAD3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C035EE-5AB2-4097-B6AF-DC3BCEA83E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="11956" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -477,9 +477,9 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.1328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.46484375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="60.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.73046875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30.06640625" bestFit="1" customWidth="1"/>
